--- a/artfynd/A 40794-2023 artfynd.xlsx
+++ b/artfynd/A 40794-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40794-2023 artfynd.xlsx
+++ b/artfynd/A 40794-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>53065765</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610227.7878685117</v>
+        <v>610228</v>
       </c>
       <c r="R8" t="n">
-        <v>6959306.905957208</v>
+        <v>6959307</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1502,19 +1502,9 @@
           <t>2012-10-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2012-10-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 40794-2023 artfynd.xlsx
+++ b/artfynd/A 40794-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>53065765</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40794-2023 artfynd.xlsx
+++ b/artfynd/A 40794-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>53065765</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 40794-2023 artfynd.xlsx
+++ b/artfynd/A 40794-2023 artfynd.xlsx
@@ -1428,7 +1428,7 @@
         <v>53065765</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
